--- a/app/src/main/assets/samples/资料分析示例.xlsx
+++ b/app/src/main/assets/samples/资料分析示例.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="题库" sheetId="1" r:id="rId1"/>
+    <sheet name="试卷" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
